--- a/base.xlsx
+++ b/base.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Simulador/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="609" documentId="8_{32D250B9-44B0-4D6A-89C9-E8E8B0ED30B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77FE3D7C-240D-4559-8250-A924CAE69731}"/>
+  <xr:revisionPtr revIDLastSave="612" documentId="8_{32D250B9-44B0-4D6A-89C9-E8E8B0ED30B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0623B13F-353E-488E-9922-8724C83C28E5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
@@ -1502,10 +1502,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15323,7 +15319,7 @@
         <v>2</v>
       </c>
       <c r="B17">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>462</v>
@@ -15575,7 +15571,7 @@
         <v>5</v>
       </c>
       <c r="B35">
-        <v>219</v>
+        <v>143</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>27</v>
@@ -15603,7 +15599,7 @@
         <v>5</v>
       </c>
       <c r="B37">
-        <v>238</v>
+        <v>72</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>26</v>
@@ -15701,7 +15697,7 @@
         <v>8</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>23</v>

--- a/base.xlsx
+++ b/base.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="612" documentId="8_{32D250B9-44B0-4D6A-89C9-E8E8B0ED30B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0623B13F-353E-488E-9922-8724C83C28E5}"/>
+  <xr:revisionPtr revIDLastSave="614" documentId="8_{32D250B9-44B0-4D6A-89C9-E8E8B0ED30B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FFF105E-0B0B-4D1F-8182-8B26BFC5C48E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="464">
   <si>
     <t>player_id</t>
   </si>
@@ -1438,6 +1438,9 @@
   </si>
   <si>
     <t>UTIL</t>
+  </si>
+  <si>
+    <t>l</t>
   </si>
 </sst>
 </file>
@@ -1502,6 +1505,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8647,8 +8654,8 @@
       <c r="F212" s="1">
         <v>3.7</v>
       </c>
-      <c r="G212" s="1">
-        <v>6.1</v>
+      <c r="G212" s="1" t="s">
+        <v>463</v>
       </c>
       <c r="H212" s="1">
         <v>1.1000000000000001</v>
@@ -15767,7 +15774,7 @@
         <v>8</v>
       </c>
       <c r="B49">
-        <v>225</v>
+        <v>59</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>27</v>

--- a/base.xlsx
+++ b/base.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filip\OneDrive\Documentos\Python Scripts\Fantasy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="614" documentId="8_{32D250B9-44B0-4D6A-89C9-E8E8B0ED30B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FFF105E-0B0B-4D1F-8182-8B26BFC5C48E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89F4572-C48D-45E9-B3DF-5F970D1886A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="2940" yWindow="1350" windowWidth="21600" windowHeight="11835" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -1505,10 +1505,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2082,25 +2078,25 @@
         <v>24</v>
       </c>
       <c r="E8" s="1">
-        <v>20.399999999999999</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1">
-        <v>11.1</v>
+        <v>12</v>
       </c>
       <c r="G8" s="1">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="H8" s="1">
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="I8" s="1">
-        <v>1.7</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J8" s="1">
         <v>0.5</v>
       </c>
       <c r="K8" s="1">
-        <v>2.1</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -3149,7 +3145,7 @@
         <v>24</v>
       </c>
       <c r="E41" s="1">
-        <v>18.100000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="F41" s="1">
         <v>7.5</v>
@@ -3164,7 +3160,7 @@
         <v>1.5</v>
       </c>
       <c r="J41" s="1">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="K41" s="1">
         <v>2.6</v>
@@ -5146,7 +5142,7 @@
         <v>26</v>
       </c>
       <c r="E103" s="1">
-        <v>16.7</v>
+        <v>19.5</v>
       </c>
       <c r="F103" s="1">
         <v>5.4</v>
@@ -5155,16 +5151,16 @@
         <v>6.4</v>
       </c>
       <c r="H103" s="1">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="I103" s="1">
         <v>0.2</v>
       </c>
       <c r="J103" s="1">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="K103" s="1">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="27" x14ac:dyDescent="0.25">
@@ -9805,10 +9801,10 @@
         <v>26</v>
       </c>
       <c r="E248" s="1">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="F248" s="1">
-        <v>3.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G248" s="1">
         <v>8.1</v>
@@ -9820,7 +9816,7 @@
         <v>0.3</v>
       </c>
       <c r="J248" s="1">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K248" s="1">
         <v>3.6</v>
